--- a/informes_data/Primera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486389_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Primera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486389_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>5.0523</v>
+        <v>4.5882</v>
       </c>
       <c r="E2" t="n">
-        <v>3.2056</v>
+        <v>2.8955</v>
       </c>
       <c r="F2" t="n">
-        <v>1.8468</v>
+        <v>1.6926</v>
       </c>
       <c r="G2" t="n">
         <v>0.3877</v>
@@ -610,13 +610,13 @@
         <v>2.1751</v>
       </c>
       <c r="S2" t="n">
-        <v>1.5123</v>
+        <v>1.0482</v>
       </c>
       <c r="T2" t="n">
-        <v>0.4062</v>
+        <v>0.0961</v>
       </c>
       <c r="U2" t="n">
-        <v>1.1061</v>
+        <v>0.952</v>
       </c>
       <c r="V2" t="n">
         <v>2.0647</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>4.4904</v>
+        <v>4.3008</v>
       </c>
       <c r="E3" t="n">
-        <v>0.6746</v>
+        <v>0.8549</v>
       </c>
       <c r="F3" t="n">
-        <v>3.8158</v>
+        <v>3.4459</v>
       </c>
       <c r="G3" t="n">
         <v>1.4773</v>
@@ -688,13 +688,13 @@
         <v>2.6101</v>
       </c>
       <c r="S3" t="n">
-        <v>0.8614000000000001</v>
+        <v>0.6717</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.4074</v>
+        <v>-0.2271</v>
       </c>
       <c r="U3" t="n">
-        <v>1.2687</v>
+        <v>0.8989</v>
       </c>
       <c r="V3" t="n">
         <v>2.8042</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.244</v>
+        <v>1.9753</v>
       </c>
       <c r="E4" t="n">
-        <v>4.1583</v>
+        <v>4.6738</v>
       </c>
       <c r="F4" t="n">
-        <v>-2.9143</v>
+        <v>-2.6986</v>
       </c>
       <c r="G4" t="n">
         <v>0.4681</v>
@@ -766,13 +766,13 @@
         <v>1.7401</v>
       </c>
       <c r="S4" t="n">
-        <v>-1.3547</v>
+        <v>-0.6234</v>
       </c>
       <c r="T4" t="n">
-        <v>-1.1644</v>
+        <v>-0.6489</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.1902</v>
+        <v>0.0255</v>
       </c>
       <c r="V4" t="n">
         <v>0.3904</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>C. POLYNICE</t>
+          <t>K. WEBSTER</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,40 +799,40 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.5654</v>
+        <v>-0.5618</v>
       </c>
       <c r="E5" t="n">
-        <v>-1.3913</v>
+        <v>0.92</v>
       </c>
       <c r="F5" t="n">
-        <v>0.8259</v>
+        <v>-1.4819</v>
       </c>
       <c r="G5" t="n">
-        <v>-2.9341</v>
+        <v>-3.4156</v>
       </c>
       <c r="H5" t="n">
-        <v>1.463</v>
+        <v>2.4453</v>
       </c>
       <c r="I5" t="n">
-        <v>-4.3971</v>
+        <v>-5.8609</v>
       </c>
       <c r="J5" t="n">
-        <v>-1.9084</v>
+        <v>0.2055</v>
       </c>
       <c r="K5" t="n">
-        <v>0.9188</v>
+        <v>2.2661</v>
       </c>
       <c r="L5" t="n">
-        <v>-2.8272</v>
+        <v>-2.0606</v>
       </c>
       <c r="M5" t="n">
-        <v>-1.0257</v>
+        <v>-3.6211</v>
       </c>
       <c r="N5" t="n">
-        <v>0.5442</v>
+        <v>0.1792</v>
       </c>
       <c r="O5" t="n">
-        <v>-1.5698</v>
+        <v>-3.8003</v>
       </c>
       <c r="P5" t="n">
         <v>1.305</v>
@@ -844,19 +844,19 @@
         <v>2.3926</v>
       </c>
       <c r="S5" t="n">
-        <v>1.0636</v>
+        <v>0.4188</v>
       </c>
       <c r="T5" t="n">
-        <v>0.4747</v>
+        <v>-0.4578</v>
       </c>
       <c r="U5" t="n">
-        <v>0.5889</v>
+        <v>0.8766</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="W5" t="n">
-        <v>1.13</v>
+        <v>2.2599</v>
       </c>
       <c r="X5" t="n">
         <v>-1.13</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>K. WEBSTER</t>
+          <t>C. POLYNICE</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,40 +877,40 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-1.1073</v>
+        <v>-0.9131</v>
       </c>
       <c r="E6" t="n">
-        <v>0.5595</v>
+        <v>-1.7698</v>
       </c>
       <c r="F6" t="n">
-        <v>-1.6668</v>
+        <v>0.8567</v>
       </c>
       <c r="G6" t="n">
-        <v>-3.4156</v>
+        <v>-2.9341</v>
       </c>
       <c r="H6" t="n">
-        <v>2.4453</v>
+        <v>1.463</v>
       </c>
       <c r="I6" t="n">
-        <v>-5.8609</v>
+        <v>-4.3971</v>
       </c>
       <c r="J6" t="n">
-        <v>0.2055</v>
+        <v>-1.9084</v>
       </c>
       <c r="K6" t="n">
-        <v>2.2661</v>
+        <v>0.9188</v>
       </c>
       <c r="L6" t="n">
-        <v>-2.0606</v>
+        <v>-2.8272</v>
       </c>
       <c r="M6" t="n">
-        <v>-3.6211</v>
+        <v>-1.0257</v>
       </c>
       <c r="N6" t="n">
-        <v>0.1792</v>
+        <v>0.5442</v>
       </c>
       <c r="O6" t="n">
-        <v>-3.8003</v>
+        <v>-1.5698</v>
       </c>
       <c r="P6" t="n">
         <v>1.305</v>
@@ -922,19 +922,19 @@
         <v>2.3926</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.1267</v>
+        <v>0.7159</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.8183</v>
+        <v>0.0961</v>
       </c>
       <c r="U6" t="n">
-        <v>0.6917</v>
+        <v>0.6198</v>
       </c>
       <c r="V6" t="n">
+        <v>0</v>
+      </c>
+      <c r="W6" t="n">
         <v>1.13</v>
-      </c>
-      <c r="W6" t="n">
-        <v>2.2599</v>
       </c>
       <c r="X6" t="n">
         <v>-1.13</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-1.9491</v>
+        <v>-1.7449</v>
       </c>
       <c r="E7" t="n">
-        <v>-2.4287</v>
+        <v>-2.3169</v>
       </c>
       <c r="F7" t="n">
-        <v>0.4796</v>
+        <v>0.572</v>
       </c>
       <c r="G7" t="n">
         <v>-1.865</v>
@@ -1000,13 +1000,13 @@
         <v>0.87</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.2364</v>
+        <v>-0.0321</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.4795</v>
+        <v>-0.3677</v>
       </c>
       <c r="U7" t="n">
-        <v>0.2431</v>
+        <v>0.3356</v>
       </c>
       <c r="V7" t="n">
         <v>0.3698</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-2.0098</v>
+        <v>-2.0406</v>
       </c>
       <c r="E8" t="n">
         <v>-1.7219</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.2879</v>
+        <v>-0.3187</v>
       </c>
       <c r="G8" t="n">
         <v>-1.2562</v>
@@ -1078,13 +1078,13 @@
         <v>0.87</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.5361</v>
+        <v>-0.5669</v>
       </c>
       <c r="T8" t="n">
         <v>-0.4795</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.0566</v>
+        <v>-0.08740000000000001</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-2.4385</v>
+        <v>-2.7554</v>
       </c>
       <c r="E9" t="n">
-        <v>0.0038</v>
+        <v>-0.3748</v>
       </c>
       <c r="F9" t="n">
-        <v>-2.4422</v>
+        <v>-2.3806</v>
       </c>
       <c r="G9" t="n">
         <v>-3.0312</v>
@@ -1156,13 +1156,13 @@
         <v>0.6525</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.0598</v>
+        <v>-0.3767</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.1454</v>
+        <v>-0.5239</v>
       </c>
       <c r="U9" t="n">
-        <v>0.0856</v>
+        <v>0.1472</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-6.3547</v>
+        <v>-6.5135</v>
       </c>
       <c r="E10" t="n">
-        <v>-4.2933</v>
+        <v>-4.113</v>
       </c>
       <c r="F10" t="n">
-        <v>-2.0614</v>
+        <v>-2.4004</v>
       </c>
       <c r="G10" t="n">
         <v>-6.0703</v>
@@ -1234,13 +1234,13 @@
         <v>0.87</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.2621</v>
+        <v>-0.4209</v>
       </c>
       <c r="T10" t="n">
-        <v>-1.0274</v>
+        <v>-0.8472</v>
       </c>
       <c r="U10" t="n">
-        <v>0.7653</v>
+        <v>0.4263</v>
       </c>
       <c r="V10" t="n">
         <v>0.1952</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-8.932399999999999</v>
+        <v>-8.2204</v>
       </c>
       <c r="E11" t="n">
-        <v>-7.8058</v>
+        <v>-7.402</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.1267</v>
+        <v>-0.8184</v>
       </c>
       <c r="G11" t="n">
         <v>-7.6184</v>
@@ -1312,13 +1312,13 @@
         <v>1.7401</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.4865</v>
+        <v>-0.7745</v>
       </c>
       <c r="T11" t="n">
-        <v>-1.3579</v>
+        <v>-0.9540999999999999</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.1286</v>
+        <v>0.1796</v>
       </c>
       <c r="V11" t="n">
         <v>1.695</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-12.5705</v>
+        <v>-11.8854</v>
       </c>
       <c r="E12" t="n">
-        <v>-9.039200000000001</v>
+        <v>-8.354200000000001</v>
       </c>
       <c r="F12" t="n">
-        <v>-3.531200000000001</v>
+        <v>-3.5314</v>
       </c>
       <c r="G12" t="n">
         <v>-23.8577</v>
@@ -1363,10 +1363,10 @@
         <v>-33.0577</v>
       </c>
       <c r="J12" t="n">
-        <v>-0.2453000000000012</v>
+        <v>-0.2453000000000021</v>
       </c>
       <c r="K12" t="n">
-        <v>9.886399999999998</v>
+        <v>9.886400000000002</v>
       </c>
       <c r="L12" t="n">
         <v>-10.1318</v>
@@ -1390,13 +1390,13 @@
         <v>16.3131</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.6249999999999998</v>
+        <v>0.06010000000000004</v>
       </c>
       <c r="T12" t="n">
-        <v>-4.9989</v>
+        <v>-4.314</v>
       </c>
       <c r="U12" t="n">
-        <v>4.374000000000001</v>
+        <v>4.3741</v>
       </c>
       <c r="V12" t="n">
         <v>8.6493</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>6.9826</v>
+        <v>7.8804</v>
       </c>
       <c r="E13" t="n">
-        <v>5.7614</v>
+        <v>6.3202</v>
       </c>
       <c r="F13" t="n">
-        <v>1.2212</v>
+        <v>1.5603</v>
       </c>
       <c r="G13" t="n">
         <v>9.5238</v>
@@ -1468,13 +1468,13 @@
         <v>1.9576</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.9985000000000001</v>
+        <v>-0.1006</v>
       </c>
       <c r="T13" t="n">
-        <v>-1.2329</v>
+        <v>-0.6741</v>
       </c>
       <c r="U13" t="n">
-        <v>0.2344</v>
+        <v>0.5735</v>
       </c>
       <c r="V13" t="n">
         <v>-1.3252</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>6.8958</v>
+        <v>6.6607</v>
       </c>
       <c r="E14" t="n">
-        <v>4.5717</v>
+        <v>4.46</v>
       </c>
       <c r="F14" t="n">
-        <v>2.324</v>
+        <v>2.2007</v>
       </c>
       <c r="G14" t="n">
         <v>4.269</v>
@@ -1546,13 +1546,13 @@
         <v>1.305</v>
       </c>
       <c r="S14" t="n">
-        <v>0.1918</v>
+        <v>-0.0433</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.4879</v>
+        <v>-0.5996</v>
       </c>
       <c r="U14" t="n">
-        <v>0.6797</v>
+        <v>0.5564</v>
       </c>
       <c r="V14" t="n">
         <v>1.13</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>4.6229</v>
+        <v>4.4404</v>
       </c>
       <c r="E15" t="n">
-        <v>2.6732</v>
+        <v>2.0027</v>
       </c>
       <c r="F15" t="n">
-        <v>1.9496</v>
+        <v>2.4377</v>
       </c>
       <c r="G15" t="n">
         <v>2.4</v>
@@ -1624,13 +1624,13 @@
         <v>1.5225</v>
       </c>
       <c r="S15" t="n">
-        <v>0.3306</v>
+        <v>0.1481</v>
       </c>
       <c r="T15" t="n">
-        <v>0.3942</v>
+        <v>-0.2764</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.0636</v>
+        <v>0.4245</v>
       </c>
       <c r="V15" t="n">
         <v>0.3698</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>B. DE BISSCHOP</t>
+          <t>D. MANCHON CRESPO</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,64 +1657,64 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.7941</v>
+        <v>1.8831</v>
       </c>
       <c r="E16" t="n">
-        <v>1.7361</v>
+        <v>0.7362</v>
       </c>
       <c r="F16" t="n">
-        <v>0.058</v>
+        <v>1.1469</v>
       </c>
       <c r="G16" t="n">
-        <v>2.9409</v>
+        <v>4.6646</v>
       </c>
       <c r="H16" t="n">
-        <v>1.5512</v>
+        <v>0.0882</v>
       </c>
       <c r="I16" t="n">
-        <v>1.3897</v>
+        <v>4.5763</v>
       </c>
       <c r="J16" t="n">
-        <v>3.914</v>
+        <v>4.3587</v>
       </c>
       <c r="K16" t="n">
-        <v>2.9961</v>
+        <v>1.3171</v>
       </c>
       <c r="L16" t="n">
-        <v>0.918</v>
+        <v>3.0416</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.9732</v>
+        <v>0.3058</v>
       </c>
       <c r="N16" t="n">
-        <v>-1.4449</v>
+        <v>-1.2289</v>
       </c>
       <c r="O16" t="n">
-        <v>0.4717</v>
+        <v>1.5347</v>
       </c>
       <c r="P16" t="n">
-        <v>0.435</v>
+        <v>-1.7401</v>
       </c>
       <c r="Q16" t="n">
-        <v>-1.0875</v>
+        <v>-3.2626</v>
       </c>
       <c r="R16" t="n">
         <v>1.5225</v>
       </c>
       <c r="S16" t="n">
-        <v>0.2877</v>
+        <v>-0.1067</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.3509</v>
+        <v>-0.5552</v>
       </c>
       <c r="U16" t="n">
-        <v>0.6385999999999999</v>
+        <v>0.4485</v>
       </c>
       <c r="V16" t="n">
-        <v>-1.8695</v>
+        <v>-0.9347</v>
       </c>
       <c r="W16" t="n">
-        <v>-0.7395</v>
+        <v>0.1952</v>
       </c>
       <c r="X16" t="n">
         <v>-1.13</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>D. MANCHON CRESPO</t>
+          <t>B. DE BISSCHOP</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,64 +1735,64 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>1.0598</v>
+        <v>1.5346</v>
       </c>
       <c r="E17" t="n">
-        <v>0.4009</v>
+        <v>1.5126</v>
       </c>
       <c r="F17" t="n">
-        <v>0.6589</v>
+        <v>0.0221</v>
       </c>
       <c r="G17" t="n">
-        <v>4.6646</v>
+        <v>2.9409</v>
       </c>
       <c r="H17" t="n">
-        <v>0.0882</v>
+        <v>1.5512</v>
       </c>
       <c r="I17" t="n">
-        <v>4.5763</v>
+        <v>1.3897</v>
       </c>
       <c r="J17" t="n">
-        <v>4.3587</v>
+        <v>3.914</v>
       </c>
       <c r="K17" t="n">
-        <v>1.3171</v>
+        <v>2.9961</v>
       </c>
       <c r="L17" t="n">
-        <v>3.0416</v>
+        <v>0.918</v>
       </c>
       <c r="M17" t="n">
-        <v>0.3058</v>
+        <v>-0.9732</v>
       </c>
       <c r="N17" t="n">
-        <v>-1.2289</v>
+        <v>-1.4449</v>
       </c>
       <c r="O17" t="n">
-        <v>1.5347</v>
+        <v>0.4717</v>
       </c>
       <c r="P17" t="n">
-        <v>-1.7401</v>
+        <v>0.435</v>
       </c>
       <c r="Q17" t="n">
-        <v>-3.2626</v>
+        <v>-1.0875</v>
       </c>
       <c r="R17" t="n">
         <v>1.5225</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.93</v>
+        <v>0.0282</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.8904</v>
+        <v>-0.5744</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.0395</v>
+        <v>0.6026</v>
       </c>
       <c r="V17" t="n">
-        <v>-0.9347</v>
+        <v>-1.8695</v>
       </c>
       <c r="W17" t="n">
-        <v>0.1952</v>
+        <v>-0.7395</v>
       </c>
       <c r="X17" t="n">
         <v>-1.13</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.3444</v>
+        <v>0.5859</v>
       </c>
       <c r="E18" t="n">
         <v>0.0182</v>
       </c>
       <c r="F18" t="n">
-        <v>0.3262</v>
+        <v>0.5677</v>
       </c>
       <c r="G18" t="n">
         <v>0.5808</v>
@@ -1858,13 +1858,13 @@
         <v>0</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.2364</v>
+        <v>0.0051</v>
       </c>
       <c r="T18" t="n">
         <v>0</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.2364</v>
+        <v>0.0051</v>
       </c>
       <c r="V18" t="n">
         <v>0</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>I. AURRECOECHEA ALCOLADO</t>
+          <t>D. STOLBETSKIY</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>0.2217</v>
+        <v>-0.0417</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.8260999999999999</v>
+        <v>-0.1845</v>
       </c>
       <c r="F19" t="n">
-        <v>1.0478</v>
+        <v>0.1427</v>
       </c>
       <c r="G19" t="n">
-        <v>1.0675</v>
+        <v>0.7418</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.09429999999999999</v>
+        <v>-0.0335</v>
       </c>
       <c r="I19" t="n">
-        <v>1.1618</v>
+        <v>0.7753</v>
       </c>
       <c r="J19" t="n">
-        <v>0.6724</v>
+        <v>0.1147</v>
       </c>
       <c r="K19" t="n">
-        <v>0.4047</v>
+        <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>0.2677</v>
+        <v>0.1147</v>
       </c>
       <c r="M19" t="n">
-        <v>0.3951</v>
+        <v>0.6271</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.4989</v>
+        <v>-0.0335</v>
       </c>
       <c r="O19" t="n">
-        <v>0.8941</v>
+        <v>0.6606</v>
       </c>
       <c r="P19" t="n">
-        <v>-0.435</v>
+        <v>0.435</v>
       </c>
       <c r="Q19" t="n">
-        <v>-1.0875</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>0.6525</v>
+        <v>0.435</v>
       </c>
       <c r="S19" t="n">
-        <v>0.9144</v>
+        <v>-0.0886</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.411</v>
+        <v>-0.2992</v>
       </c>
       <c r="U19" t="n">
-        <v>1.3253</v>
+        <v>0.2106</v>
       </c>
       <c r="V19" t="n">
-        <v>-1.3252</v>
+        <v>-1.13</v>
       </c>
       <c r="W19" t="n">
         <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>-1.3252</v>
+        <v>-1.13</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>D. STOLBETSKIY</t>
+          <t>I. AURRECOECHEA ALCOLADO</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,67 +1969,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.3693</v>
+        <v>-0.09030000000000001</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.2962</v>
+        <v>-0.4908</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.073</v>
+        <v>0.4005</v>
       </c>
       <c r="G20" t="n">
-        <v>0.7418</v>
+        <v>1.0675</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.0335</v>
+        <v>-0.09429999999999999</v>
       </c>
       <c r="I20" t="n">
-        <v>0.7753</v>
+        <v>1.1618</v>
       </c>
       <c r="J20" t="n">
-        <v>0.1147</v>
+        <v>0.6724</v>
       </c>
       <c r="K20" t="n">
-        <v>0</v>
+        <v>0.4047</v>
       </c>
       <c r="L20" t="n">
-        <v>0.1147</v>
+        <v>0.2677</v>
       </c>
       <c r="M20" t="n">
-        <v>0.6271</v>
+        <v>0.3951</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.0335</v>
+        <v>-0.4989</v>
       </c>
       <c r="O20" t="n">
-        <v>0.6606</v>
+        <v>0.8941</v>
       </c>
       <c r="P20" t="n">
-        <v>0.435</v>
+        <v>-0.435</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>-1.0875</v>
       </c>
       <c r="R20" t="n">
-        <v>0.435</v>
+        <v>0.6525</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.4161</v>
+        <v>0.6022999999999999</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.411</v>
+        <v>-0.0757</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.0052</v>
+        <v>0.678</v>
       </c>
       <c r="V20" t="n">
-        <v>-1.13</v>
+        <v>-1.3252</v>
       </c>
       <c r="W20" t="n">
         <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>-1.13</v>
+        <v>-1.3252</v>
       </c>
     </row>
     <row r="21">
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.7333</v>
+        <v>-0.6446</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.2961</v>
+        <v>-0.9608</v>
       </c>
       <c r="F21" t="n">
-        <v>0.5628</v>
+        <v>0.3163</v>
       </c>
       <c r="G21" t="n">
         <v>1.4345</v>
@@ -2092,13 +2092,13 @@
         <v>1.305</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.1884</v>
+        <v>-0.0997</v>
       </c>
       <c r="T21" t="n">
-        <v>-1.1644</v>
+        <v>-0.8292</v>
       </c>
       <c r="U21" t="n">
-        <v>0.976</v>
+        <v>0.7294</v>
       </c>
       <c r="V21" t="n">
         <v>-1.1093</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-3.2487</v>
+        <v>-4.198</v>
       </c>
       <c r="E22" t="n">
-        <v>-3.9379</v>
+        <v>-4.9437</v>
       </c>
       <c r="F22" t="n">
-        <v>0.6892</v>
+        <v>0.7458</v>
       </c>
       <c r="G22" t="n">
         <v>-1.3741</v>
@@ -2170,13 +2170,13 @@
         <v>1.7401</v>
       </c>
       <c r="S22" t="n">
-        <v>1.9079</v>
+        <v>0.9587</v>
       </c>
       <c r="T22" t="n">
-        <v>1.0022</v>
+        <v>-0.0036</v>
       </c>
       <c r="U22" t="n">
-        <v>0.9056999999999999</v>
+        <v>0.9622000000000001</v>
       </c>
       <c r="V22" t="n">
         <v>-2.2599</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-4.9995</v>
+        <v>-4.6951</v>
       </c>
       <c r="E23" t="n">
-        <v>-5.2739</v>
+        <v>-4.9386</v>
       </c>
       <c r="F23" t="n">
-        <v>0.2744</v>
+        <v>0.2436</v>
       </c>
       <c r="G23" t="n">
         <v>-2.3912</v>
@@ -2248,13 +2248,13 @@
         <v>1.0875</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.2381</v>
+        <v>0.0664</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.822</v>
+        <v>-0.4867</v>
       </c>
       <c r="U23" t="n">
-        <v>0.5839</v>
+        <v>0.5531</v>
       </c>
       <c r="V23" t="n">
         <v>-0.1952</v>
@@ -2281,25 +2281,25 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>12.5705</v>
+        <v>13.3154</v>
       </c>
       <c r="E24" t="n">
-        <v>3.531299999999999</v>
+        <v>3.5315</v>
       </c>
       <c r="F24" t="n">
-        <v>9.039099999999999</v>
+        <v>9.784300000000002</v>
       </c>
       <c r="G24" t="n">
         <v>23.8576</v>
       </c>
       <c r="H24" t="n">
-        <v>-9.200099999999999</v>
+        <v>-9.200100000000001</v>
       </c>
       <c r="I24" t="n">
         <v>33.0575</v>
       </c>
       <c r="J24" t="n">
-        <v>23.61190000000001</v>
+        <v>23.6119</v>
       </c>
       <c r="K24" t="n">
         <v>0.6862999999999995</v>
@@ -2326,19 +2326,19 @@
         <v>13.0502</v>
       </c>
       <c r="S24" t="n">
-        <v>0.6248999999999998</v>
+        <v>1.3699</v>
       </c>
       <c r="T24" t="n">
-        <v>-4.374099999999999</v>
+        <v>-4.3741</v>
       </c>
       <c r="U24" t="n">
-        <v>4.998899999999999</v>
+        <v>5.7439</v>
       </c>
       <c r="V24" t="n">
         <v>-8.6492</v>
       </c>
       <c r="W24" t="n">
-        <v>0.6063999999999998</v>
+        <v>0.6063999999999996</v>
       </c>
       <c r="X24" t="n">
         <v>-9.255699999999999</v>
